--- a/Docs/Source to target mapping.xlsx
+++ b/Docs/Source to target mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20384"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ZinukovD\source\repos\Northwind_BI_Solution\Docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zinyk\source\repos\Northwind_BI_Solution\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1886F2E7-3FF5-4AA5-B8B8-AFB8F731415E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2497363C-E546-46FB-A024-5AA919F212D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="558" activeTab="3" xr2:uid="{4088A55A-653F-450D-AAB8-4D657457B3B6}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="558" activeTab="1" xr2:uid="{4088A55A-653F-450D-AAB8-4D657457B3B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Customer" sheetId="2" r:id="rId1"/>
@@ -1024,27 +1024,6 @@
     <t>NOT LOOKUP HASH TABLE</t>
   </si>
   <si>
-    <t>CHECKSUM ( [CompanyName], [ContactName], [ContactTitle], [City], [Country], [Phone], [Fax] )</t>
-  </si>
-  <si>
-    <t>CHECKSUM ( [Date], [DateType], [HolidayName] )</t>
-  </si>
-  <si>
-    <t>CHECKSUM ( [LastName], [FirstName], [Title], [TitleOfCourtesy], [City], [Country] )</t>
-  </si>
-  <si>
-    <t>CHECKSUM ( [ProductName], [CategoryID] )</t>
-  </si>
-  <si>
-    <t>CHECKSUM ( [CategoryName] )</t>
-  </si>
-  <si>
-    <t>CHECKSUM ( [CustomerID], [EmployeeID], [OrderDate], [RequiredDate], [ShippedDate] )</t>
-  </si>
-  <si>
-    <t>CHECKSUM ( [UnitPrice], [Quantity], [Discount] )</t>
-  </si>
-  <si>
     <t>Lookup OrderID in Order Details &amp; Lookup ProductKey in Dimension.Product</t>
   </si>
   <si>
@@ -1121,6 +1100,27 @@
 			FOR JSON PATH, WITHOUT_ARRAY_WRAPPER
 		)
 (DT_NTEXT)"{\"MDS\":[{\"mdm_masterProduct\":" + (ISNULL(MasterProductAllAttributes) ? (DT_NTEXT)"{}" : MasterProductAllAttributes) + (DT_NTEXT)"}],\"DQS\":[{\"dbo_NW_Products\":" + (ISNULL(DQSProductAllAttributes) ? (DT_NTEXT)"{}" : DQSProductAllAttributes) + (DT_NTEXT)"},{\"dbo_NW_Categories\":" + (ISNULL(DQSCategoryAllAttributes) ? (DT_NTEXT)"{}" : DQSCategoryAllAttributes) + (DT_NTEXT)"}]}"</t>
+  </si>
+  <si>
+    <t>CAST ( HASHBYTES ( N'SHA2_512', CONCAT ( ISNULL ( [DateType], N'' ), N'#', ISNULL ( [HolidayName], N'' ) ) ) AS VARBINARY(64) )</t>
+  </si>
+  <si>
+    <t>CAST ( HASHBYTES ( N'SHA2_512', CONCAT ( ISNULL ( [CompanyName], N'' ), N'#', ISNULL ( [ContactName], N'' ), N'#', ISNULL ( [ContactTitle], N'' ), N'#', ISNULL ( [City], N'' ), N'#', ISNULL ( [Country], N'' ), N'#', ISNULL ( [Phone], N'' ), N'#', ISNULL ( [Fax], N'' ) ) ) AS VARBINARY(64) )</t>
+  </si>
+  <si>
+    <t>CAST ( HASHBYTES ( N'SHA2_512', CONCAT ( ISNULL ( [LastName], N'' ), N'#', ISNULL ( [FirstName], N'' ), N'#', ISNULL ( [Title], N'' ), N'#', ISNULL ( [TitleOfCourtesy], N'' ), N'#', ISNULL ( [City], N'' ), N'#', ISNULL ( [Country], N'' ) ) ) AS VARBINARY(64) )</t>
+  </si>
+  <si>
+    <t>CAST ( HASHBYTES ( N'SHA2_512', CONCAT ( ISNULL ( [ProductName], N'' ), N'#', ISNULL ( [CategoryID], 0 ) ) ) AS VARBINARY(64) )</t>
+  </si>
+  <si>
+    <t>CAST ( HASHBYTES ( N'SHA2_512', ISNULL ( [CategoryName], N'' ) ) AS VARBINARY(64) )</t>
+  </si>
+  <si>
+    <t>CAST ( HASHBYTES ( N'SHA2_512', CONCAT ( ISNULL ( [CustomerID], CAST ( N'' AS NCHAR(5) ) ), N'#', ISNULL ( [EmployeeID], 0 ), N'#', ISNULL ( [OrderDate], DATEFROMPARTS ( 1995, 12, 31 ) ), N'#', ISNULL ( [RequiredDate], DATEFROMPARTS ( 1995, 12, 31 ) ), N'#', ISNULL ( [ShippedDate], DATEFROMPARTS ( 1995, 12, 31 ) ) ) ) AS VARBINARY(64) )</t>
+  </si>
+  <si>
+    <t>CAST ( HASHBYTES ( N'SHA2_512', CONCAT ( ISNULL ( [UnitPrice], CAST ( 0 AS MONEY ) ), N'#', ISNULL ( [Quantity], CAST ( 0 AS SMALLINT ) ), N'#', ISNULL ( [Discount], CAST ( 0 AS REAL ) ) ) ) AS VARBINARY(64) )</t>
   </si>
 </sst>
 </file>
@@ -1371,13 +1371,24 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1389,22 +1400,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="20% - Accent1" xfId="3" builtinId="30"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="20% — акцент1" xfId="3" builtinId="30"/>
     <cellStyle name="Акцент3 2" xfId="2" xr:uid="{72B9F317-F5C0-45A7-AA7C-0F44C45D1FF6}"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{A125878E-94C1-497A-B7A1-BCB52D1AE9BA}"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1421,9 +1421,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1461,7 +1461,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1567,7 +1567,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1709,7 +1709,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1752,47 +1752,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="34" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="33" t="s">
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="34" t="s">
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="33" t="s">
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="32" t="s">
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="32"/>
-      <c r="AC1" s="32"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
     </row>
     <row r="2" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
@@ -2527,16 +2527,16 @@
         <v>10</v>
       </c>
       <c r="Z12" t="s">
-        <v>341</v>
-      </c>
-      <c r="AA12" s="41" t="s">
+        <v>334</v>
+      </c>
+      <c r="AA12" s="32" t="s">
         <v>61</v>
       </c>
       <c r="AB12" t="s">
         <v>12</v>
       </c>
-      <c r="AC12" s="42" t="s">
-        <v>342</v>
+      <c r="AC12" s="33" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.25">
@@ -2717,7 +2717,7 @@
         <v>325</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -4652,47 +4652,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="36" t="s">
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="35" t="s">
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="40" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="36" t="s">
+      <c r="K1" s="40"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="36"/>
-      <c r="R1" s="36"/>
-      <c r="S1" s="36"/>
-      <c r="T1" s="35" t="s">
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+      <c r="T1" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="37" t="s">
+      <c r="U1" s="40"/>
+      <c r="V1" s="40"/>
+      <c r="W1" s="40"/>
+      <c r="X1" s="40"/>
+      <c r="Y1" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="37"/>
-      <c r="AA1" s="37"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="37"/>
+      <c r="Z1" s="42"/>
+      <c r="AA1" s="42"/>
+      <c r="AB1" s="42"/>
+      <c r="AC1" s="42"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
@@ -6352,7 +6352,7 @@
         <v>325</v>
       </c>
       <c r="I40" s="24" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="J40" s="26"/>
       <c r="K40" s="26"/>
@@ -7585,47 +7585,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="34" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="33" t="s">
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="38" t="s">
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="39"/>
-      <c r="S1" s="40"/>
-      <c r="T1" s="33" t="s">
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="32" t="s">
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="32"/>
-      <c r="AC1" s="32"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
     </row>
     <row r="2" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
@@ -8194,16 +8194,16 @@
         <v>185</v>
       </c>
       <c r="Z10" t="s">
-        <v>341</v>
-      </c>
-      <c r="AA10" s="41" t="s">
+        <v>334</v>
+      </c>
+      <c r="AA10" s="32" t="s">
         <v>61</v>
       </c>
       <c r="AB10" t="s">
         <v>12</v>
       </c>
-      <c r="AC10" s="42" t="s">
-        <v>343</v>
+      <c r="AC10" s="33" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
@@ -8518,7 +8518,7 @@
         <v>325</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -10306,47 +10306,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="34" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="33" t="s">
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="38" t="s">
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="39"/>
-      <c r="S1" s="40"/>
-      <c r="T1" s="33" t="s">
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="U1" s="33"/>
-      <c r="V1" s="33"/>
-      <c r="W1" s="33"/>
-      <c r="X1" s="33"/>
-      <c r="Y1" s="32" t="s">
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="32"/>
-      <c r="AC1" s="32"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
     </row>
     <row r="2" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
@@ -10691,7 +10691,7 @@
         <v>57</v>
       </c>
       <c r="X6" s="29" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="Y6" s="10" t="s">
         <v>221</v>
@@ -10736,16 +10736,16 @@
         <v>221</v>
       </c>
       <c r="Z7" t="s">
-        <v>341</v>
-      </c>
-      <c r="AA7" s="41" t="s">
+        <v>334</v>
+      </c>
+      <c r="AA7" s="32" t="s">
         <v>61</v>
       </c>
       <c r="AB7" t="s">
         <v>12</v>
       </c>
-      <c r="AC7" s="42" t="s">
-        <v>344</v>
+      <c r="AC7" s="33" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
@@ -10895,7 +10895,7 @@
         <v>325</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
@@ -12291,7 +12291,7 @@
         <v>325</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
@@ -12801,26 +12801,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="34" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="33" t="s">
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
@@ -12929,7 +12929,7 @@
         <v>301</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -12969,7 +12969,7 @@
         <v>302</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -13009,7 +13009,7 @@
         <v>303</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -13149,7 +13149,7 @@
         <v>300</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -13175,7 +13175,7 @@
         <v>300</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -13201,7 +13201,7 @@
         <v>300</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -13227,7 +13227,7 @@
         <v>300</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -13253,7 +13253,7 @@
         <v>300</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -13358,7 +13358,7 @@
         <v>325</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
@@ -13544,7 +13544,7 @@
         <v>325</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>

--- a/Docs/Source to target mapping.xlsx
+++ b/Docs/Source to target mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zinyk\source\repos\Northwind_BI_Solution\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2497363C-E546-46FB-A024-5AA919F212D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C8D7EF-1870-4FD2-AD5B-3DC32A428228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="558" activeTab="1" xr2:uid="{4088A55A-653F-450D-AAB8-4D657457B3B6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="558" activeTab="1" xr2:uid="{4088A55A-653F-450D-AAB8-4D657457B3B6}"/>
   </bookViews>
   <sheets>
     <sheet name="Customer" sheetId="2" r:id="rId1"/>
@@ -497,9 +497,6 @@
     <t>DateType_Name</t>
   </si>
   <si>
-    <t>NOT NULL &amp; Date = AlterDateKey</t>
-  </si>
-  <si>
     <t>Holidays</t>
   </si>
   <si>
@@ -1121,6 +1118,9 @@
   </si>
   <si>
     <t>CAST ( HASHBYTES ( N'SHA2_512', CONCAT ( ISNULL ( [UnitPrice], CAST ( 0 AS MONEY ) ), N'#', ISNULL ( [Quantity], CAST ( 0 AS SMALLINT ) ), N'#', ISNULL ( [Discount], CAST ( 0 AS REAL ) ) ) ) AS VARBINARY(64) )</t>
+  </si>
+  <si>
+    <t>NOT NULL &amp; Date = DateKey</t>
   </si>
 </sst>
 </file>
@@ -1373,13 +1373,22 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1390,15 +1399,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1752,47 +1752,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="35" t="s">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="34" t="s">
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="35" t="s">
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="39" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="34" t="s">
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="39"/>
+      <c r="S1" s="39"/>
+      <c r="T1" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="36" t="s">
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="36"/>
-      <c r="AA1" s="36"/>
-      <c r="AB1" s="36"/>
-      <c r="AC1" s="36"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
     </row>
     <row r="2" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
@@ -1960,7 +1960,7 @@
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
       <c r="O4" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P4" s="3" t="s">
         <v>37</v>
@@ -2033,7 +2033,7 @@
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
       <c r="O5" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P5" s="3" t="s">
         <v>13</v>
@@ -2108,7 +2108,7 @@
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
       <c r="O6" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P6" s="3" t="s">
         <v>24</v>
@@ -2179,7 +2179,7 @@
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
       <c r="O7" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P7" s="3" t="s">
         <v>25</v>
@@ -2250,7 +2250,7 @@
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
       <c r="O8" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>14</v>
@@ -2321,7 +2321,7 @@
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
       <c r="O9" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>15</v>
@@ -2392,7 +2392,7 @@
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
       <c r="O10" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>16</v>
@@ -2463,7 +2463,7 @@
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
       <c r="O11" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P11" s="3" t="s">
         <v>26</v>
@@ -2527,7 +2527,7 @@
         <v>10</v>
       </c>
       <c r="Z12" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AA12" s="32" t="s">
         <v>61</v>
@@ -2536,7 +2536,7 @@
         <v>12</v>
       </c>
       <c r="AC12" s="33" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.25">
@@ -2708,16 +2708,16 @@
         <v>116</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>29</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -3977,17 +3977,17 @@
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
       <c r="O51" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q51" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="R51" s="3"/>
       <c r="S51" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="T51" s="5"/>
       <c r="U51" s="5"/>
@@ -4016,17 +4016,17 @@
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
       <c r="O52" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q52" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="R52" s="3"/>
       <c r="S52" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="T52" s="5"/>
       <c r="U52" s="5"/>
@@ -4055,17 +4055,17 @@
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
       <c r="O53" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="T53" s="5"/>
       <c r="U53" s="5"/>
@@ -4646,53 +4646,53 @@
     <col min="25" max="25" width="5.85546875" style="15" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="20.85546875" style="15" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="15.5703125" style="15" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="30.5703125" style="15" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="26" style="15" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="69.42578125" style="15" customWidth="1"/>
     <col min="30" max="16384" width="8.85546875" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="40"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="41" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="40" t="s">
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="40"/>
-      <c r="L1" s="40"/>
-      <c r="M1" s="40"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="41" t="s">
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="41"/>
-      <c r="T1" s="40" t="s">
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="U1" s="40"/>
-      <c r="V1" s="40"/>
-      <c r="W1" s="40"/>
-      <c r="X1" s="40"/>
-      <c r="Y1" s="42" t="s">
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="42"/>
-      <c r="AA1" s="42"/>
-      <c r="AB1" s="42"/>
-      <c r="AC1" s="42"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
@@ -5754,10 +5754,10 @@
         <v>55</v>
       </c>
       <c r="AB27" s="21" t="s">
-        <v>153</v>
+        <v>344</v>
       </c>
       <c r="AC27" s="21" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="28" spans="1:29" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5795,10 +5795,10 @@
         <v>32</v>
       </c>
       <c r="AB28" s="21" t="s">
-        <v>153</v>
+        <v>344</v>
       </c>
       <c r="AC28" s="23" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="29" spans="1:29" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -5836,31 +5836,31 @@
         <v>147</v>
       </c>
       <c r="AB29" s="21" t="s">
-        <v>153</v>
+        <v>344</v>
       </c>
       <c r="AC29" s="23" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="C30" s="19" t="s">
         <v>311</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="D30" s="19" t="s">
         <v>175</v>
-      </c>
-      <c r="C30" s="19" t="s">
-        <v>312</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>176</v>
       </c>
       <c r="E30" s="20"/>
       <c r="F30" s="20"/>
       <c r="G30" s="20"/>
       <c r="H30" s="20"/>
       <c r="I30" s="20" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="J30" s="19"/>
       <c r="K30" s="19"/>
@@ -5885,33 +5885,33 @@
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B31" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="D31" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="C31" s="19" t="s">
-        <v>178</v>
-      </c>
-      <c r="D31" s="19" t="s">
-        <v>176</v>
-      </c>
       <c r="E31" s="20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H31" s="20"/>
       <c r="I31" s="20"/>
       <c r="J31" s="19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K31" s="19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L31" s="19" t="s">
         <v>61</v>
@@ -5919,7 +5919,7 @@
       <c r="M31" s="19"/>
       <c r="N31" s="19"/>
       <c r="O31" s="24" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P31" s="20" t="s">
         <v>13</v>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="R31" s="20"/>
       <c r="S31" s="20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="T31" s="19" t="s">
         <v>150</v>
@@ -5950,16 +5950,16 @@
     </row>
     <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B32" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="D32" s="19" t="s">
         <v>175</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>313</v>
-      </c>
-      <c r="D32" s="19" t="s">
-        <v>176</v>
       </c>
       <c r="E32" s="20"/>
       <c r="F32" s="20"/>
@@ -5989,19 +5989,19 @@
     </row>
     <row r="33" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F33" s="20" t="s">
         <v>118</v>
@@ -6013,13 +6013,13 @@
         <v>12</v>
       </c>
       <c r="I33" s="20" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J33" s="19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K33" s="19" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L33" s="19" t="s">
         <v>146</v>
@@ -6027,7 +6027,7 @@
       <c r="M33" s="19"/>
       <c r="N33" s="19"/>
       <c r="O33" s="24" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P33" s="20" t="s">
         <v>37</v>
@@ -6037,7 +6037,7 @@
       </c>
       <c r="R33" s="20"/>
       <c r="S33" s="20" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="T33" s="19" t="s">
         <v>150</v>
@@ -6058,22 +6058,22 @@
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E34" s="20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G34" s="20" t="s">
         <v>147</v>
@@ -6082,13 +6082,13 @@
         <v>12</v>
       </c>
       <c r="I34" s="20" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J34" s="19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K34" s="19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="L34" s="19" t="s">
         <v>147</v>
@@ -6096,17 +6096,17 @@
       <c r="M34" s="19"/>
       <c r="N34" s="19"/>
       <c r="O34" s="24" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P34" s="20" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q34" s="24" t="s">
         <v>39</v>
       </c>
       <c r="R34" s="20"/>
       <c r="S34" s="20" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="T34" s="19" t="s">
         <v>150</v>
@@ -6141,7 +6141,7 @@
       <c r="M35" s="19"/>
       <c r="N35" s="19"/>
       <c r="O35" s="24" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P35" s="20" t="s">
         <v>118</v>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="R35" s="20"/>
       <c r="S35" s="20" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="T35" s="19" t="s">
         <v>150</v>
@@ -6186,13 +6186,13 @@
       <c r="M36" s="19"/>
       <c r="N36" s="19"/>
       <c r="O36" s="24" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P36" s="20" t="s">
         <v>145</v>
       </c>
       <c r="Q36" s="20" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="R36" s="20"/>
       <c r="S36" s="20"/>
@@ -6203,11 +6203,11 @@
         <v>145</v>
       </c>
       <c r="V36" s="19" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="W36" s="19"/>
       <c r="X36" s="25" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Y36" s="21"/>
       <c r="Z36" s="21"/>
@@ -6217,23 +6217,23 @@
     </row>
     <row r="37" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E37" s="20"/>
       <c r="F37" s="20"/>
       <c r="G37" s="20"/>
       <c r="H37" s="20"/>
       <c r="I37" s="20" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="J37" s="19"/>
       <c r="K37" s="19"/>
@@ -6258,16 +6258,16 @@
     </row>
     <row r="38" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E38" s="20"/>
       <c r="F38" s="20"/>
@@ -6297,16 +6297,16 @@
     </row>
     <row r="39" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E39" s="20"/>
       <c r="F39" s="20"/>
@@ -6340,19 +6340,19 @@
       <c r="C40" s="26"/>
       <c r="D40" s="26"/>
       <c r="E40" s="20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F40" s="24" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G40" s="24" t="s">
         <v>29</v>
       </c>
       <c r="H40" s="24" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I40" s="24" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="J40" s="26"/>
       <c r="K40" s="26"/>
@@ -6386,10 +6386,10 @@
       <c r="H41" s="20"/>
       <c r="I41" s="20"/>
       <c r="J41" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="K41" s="28" t="s">
         <v>154</v>
-      </c>
-      <c r="K41" s="28" t="s">
-        <v>155</v>
       </c>
       <c r="L41" s="28" t="s">
         <v>146</v>
@@ -6423,10 +6423,10 @@
       <c r="H42" s="20"/>
       <c r="I42" s="20"/>
       <c r="J42" s="28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K42" s="28" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L42" s="28" t="s">
         <v>61</v>
@@ -6460,10 +6460,10 @@
       <c r="H43" s="20"/>
       <c r="I43" s="20"/>
       <c r="J43" s="28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K43" s="28" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L43" s="28" t="s">
         <v>61</v>
@@ -6497,10 +6497,10 @@
       <c r="H44" s="20"/>
       <c r="I44" s="20"/>
       <c r="J44" s="28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K44" s="28" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L44" s="28" t="s">
         <v>61</v>
@@ -6534,10 +6534,10 @@
       <c r="H45" s="20"/>
       <c r="I45" s="20"/>
       <c r="J45" s="28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K45" s="28" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L45" s="28" t="s">
         <v>147</v>
@@ -6571,10 +6571,10 @@
       <c r="H46" s="20"/>
       <c r="I46" s="20"/>
       <c r="J46" s="28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K46" s="28" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L46" s="28" t="s">
         <v>61</v>
@@ -6608,10 +6608,10 @@
       <c r="H47" s="20"/>
       <c r="I47" s="20"/>
       <c r="J47" s="28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K47" s="28" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L47" s="28" t="s">
         <v>61</v>
@@ -6645,10 +6645,10 @@
       <c r="H48" s="20"/>
       <c r="I48" s="20"/>
       <c r="J48" s="28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K48" s="28" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L48" s="28" t="s">
         <v>61</v>
@@ -6682,13 +6682,13 @@
       <c r="H49" s="20"/>
       <c r="I49" s="20"/>
       <c r="J49" s="28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K49" s="28" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L49" s="28" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M49" s="19"/>
       <c r="N49" s="19"/>
@@ -6719,10 +6719,10 @@
       <c r="H50" s="20"/>
       <c r="I50" s="20"/>
       <c r="J50" s="28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K50" s="28" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L50" s="28" t="s">
         <v>61</v>
@@ -6756,10 +6756,10 @@
       <c r="H51" s="20"/>
       <c r="I51" s="20"/>
       <c r="J51" s="28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K51" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L51" s="28" t="s">
         <v>61</v>
@@ -6793,10 +6793,10 @@
       <c r="H52" s="20"/>
       <c r="I52" s="20"/>
       <c r="J52" s="28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K52" s="28" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L52" s="28" t="s">
         <v>61</v>
@@ -6830,7 +6830,7 @@
       <c r="H53" s="20"/>
       <c r="I53" s="20"/>
       <c r="J53" s="28" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K53" s="28" t="s">
         <v>101</v>
@@ -6872,17 +6872,17 @@
       <c r="M54" s="19"/>
       <c r="N54" s="19"/>
       <c r="O54" s="24" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P54" s="24" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q54" s="24" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="R54" s="24"/>
       <c r="S54" s="24" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="T54" s="19"/>
       <c r="U54" s="19"/>
@@ -6911,17 +6911,17 @@
       <c r="M55" s="19"/>
       <c r="N55" s="19"/>
       <c r="O55" s="24" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P55" s="24" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q55" s="24" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="R55" s="24"/>
       <c r="S55" s="24" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="T55" s="19"/>
       <c r="U55" s="19"/>
@@ -6950,17 +6950,17 @@
       <c r="M56" s="19"/>
       <c r="N56" s="19"/>
       <c r="O56" s="24" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P56" s="24" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q56" s="24" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="R56" s="24"/>
       <c r="S56" s="24" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="T56" s="19"/>
       <c r="U56" s="19"/>
@@ -7585,47 +7585,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="35" t="s">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="34" t="s">
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="37" t="s">
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="34" t="s">
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="36" t="s">
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="36"/>
-      <c r="AA1" s="36"/>
-      <c r="AB1" s="36"/>
-      <c r="AC1" s="36"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
     </row>
     <row r="2" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
@@ -7742,10 +7742,10 @@
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
       <c r="Y3" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Z3" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AA3" s="10" t="s">
         <v>29</v>
@@ -7762,19 +7762,19 @@
         <v>117</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>219</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>220</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>29</v>
@@ -7784,20 +7784,20 @@
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P4" s="3" t="s">
         <v>37</v>
@@ -7808,7 +7808,7 @@
       <c r="R4" s="10"/>
       <c r="S4" s="10"/>
       <c r="T4" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U4" s="5" t="s">
         <v>37</v>
@@ -7819,10 +7819,10 @@
       <c r="W4" s="5"/>
       <c r="X4" s="5"/>
       <c r="Y4" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Z4" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AA4" s="10" t="s">
         <v>29</v>
@@ -7853,7 +7853,7 @@
       <c r="R5" s="13"/>
       <c r="S5" s="10"/>
       <c r="T5" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U5" s="5" t="s">
         <v>13</v>
@@ -7865,16 +7865,16 @@
         <v>57</v>
       </c>
       <c r="X5" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Y5" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Z5" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AA5" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AB5" s="10" t="s">
         <v>12</v>
@@ -7886,19 +7886,19 @@
         <v>117</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>33</v>
@@ -7906,23 +7906,23 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L6" s="5" t="s">
         <v>61</v>
       </c>
       <c r="M6" s="5"/>
       <c r="N6" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>33</v>
@@ -7930,10 +7930,10 @@
       <c r="R6" s="10"/>
       <c r="S6" s="10"/>
       <c r="T6" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U6" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="V6" s="5" t="s">
         <v>33</v>
@@ -7941,10 +7941,10 @@
       <c r="W6" s="5"/>
       <c r="X6" s="5"/>
       <c r="Y6" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z6" s="10" t="s">
         <v>185</v>
-      </c>
-      <c r="Z6" s="10" t="s">
-        <v>186</v>
       </c>
       <c r="AA6" s="10" t="s">
         <v>33</v>
@@ -7957,19 +7957,19 @@
         <v>117</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>149</v>
@@ -7977,23 +7977,23 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>61</v>
       </c>
       <c r="M7" s="5"/>
       <c r="N7" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>149</v>
@@ -8001,10 +8001,10 @@
       <c r="R7" s="10"/>
       <c r="S7" s="10"/>
       <c r="T7" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U7" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="V7" s="5" t="s">
         <v>149</v>
@@ -8012,10 +8012,10 @@
       <c r="W7" s="5"/>
       <c r="X7" s="5"/>
       <c r="Y7" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Z7" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AA7" s="10" t="s">
         <v>149</v>
@@ -8028,7 +8028,7 @@
         <v>117</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>14</v>
@@ -8037,7 +8037,7 @@
         <v>104</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>14</v>
@@ -8048,7 +8048,7 @@
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>65</v>
@@ -8061,7 +8061,7 @@
         <v>111</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P8" s="3" t="s">
         <v>14</v>
@@ -8072,7 +8072,7 @@
       <c r="R8" s="10"/>
       <c r="S8" s="10"/>
       <c r="T8" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U8" s="5" t="s">
         <v>14</v>
@@ -8083,7 +8083,7 @@
       <c r="W8" s="5"/>
       <c r="X8" s="5"/>
       <c r="Y8" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Z8" s="10" t="s">
         <v>14</v>
@@ -8099,7 +8099,7 @@
         <v>117</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>15</v>
@@ -8108,7 +8108,7 @@
         <v>104</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>15</v>
@@ -8119,7 +8119,7 @@
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>66</v>
@@ -8132,7 +8132,7 @@
         <v>110</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>15</v>
@@ -8143,7 +8143,7 @@
       <c r="R9" s="10"/>
       <c r="S9" s="10"/>
       <c r="T9" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U9" s="5" t="s">
         <v>15</v>
@@ -8154,7 +8154,7 @@
       <c r="W9" s="5"/>
       <c r="X9" s="5"/>
       <c r="Y9" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Z9" s="10" t="s">
         <v>15</v>
@@ -8191,10 +8191,10 @@
       <c r="W10" s="5"/>
       <c r="X10" s="5"/>
       <c r="Y10" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Z10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AA10" s="32" t="s">
         <v>61</v>
@@ -8203,7 +8203,7 @@
         <v>12</v>
       </c>
       <c r="AC10" s="33" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.25">
@@ -8232,7 +8232,7 @@
       <c r="W11" s="5"/>
       <c r="X11" s="5"/>
       <c r="Y11" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Z11" s="10" t="s">
         <v>18</v>
@@ -8273,7 +8273,7 @@
       <c r="W12" s="5"/>
       <c r="X12" s="5"/>
       <c r="Y12" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Z12" s="10" t="s">
         <v>19</v>
@@ -8312,7 +8312,7 @@
       <c r="W13" s="5"/>
       <c r="X13" s="5"/>
       <c r="Y13" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Z13" s="10" t="s">
         <v>27</v>
@@ -8353,7 +8353,7 @@
       <c r="W14" s="5"/>
       <c r="X14" s="5"/>
       <c r="Y14" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Z14" s="10" t="s">
         <v>28</v>
@@ -8371,59 +8371,59 @@
         <v>117</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>61</v>
       </c>
       <c r="M15" s="5"/>
       <c r="N15" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="R15" s="10"/>
       <c r="S15" s="10"/>
       <c r="T15" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="U15" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="V15" s="5" t="s">
         <v>191</v>
-      </c>
-      <c r="U15" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="V15" s="5" t="s">
-        <v>192</v>
       </c>
       <c r="W15" s="5"/>
       <c r="X15" s="5"/>
@@ -8438,59 +8438,59 @@
         <v>117</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>149</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L16" s="5" t="s">
         <v>61</v>
       </c>
       <c r="M16" s="5"/>
       <c r="N16" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="R16" s="10"/>
       <c r="S16" s="10"/>
       <c r="T16" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="U16" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="V16" s="5" t="s">
         <v>191</v>
-      </c>
-      <c r="U16" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="V16" s="5" t="s">
-        <v>192</v>
       </c>
       <c r="W16" s="5"/>
       <c r="X16" s="5"/>
@@ -8506,19 +8506,19 @@
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>29</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -8552,10 +8552,10 @@
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="K18" s="8" t="s">
         <v>193</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>194</v>
       </c>
       <c r="L18" s="8" t="s">
         <v>29</v>
@@ -8589,10 +8589,10 @@
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L19" s="8" t="s">
         <v>61</v>
@@ -8626,10 +8626,10 @@
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L20" s="8" t="s">
         <v>61</v>
@@ -8663,10 +8663,10 @@
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L21" s="8" t="s">
         <v>61</v>
@@ -8700,13 +8700,13 @@
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
@@ -8737,10 +8737,10 @@
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L23" s="8" t="s">
         <v>61</v>
@@ -8774,10 +8774,10 @@
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="L24" s="8" t="s">
         <v>61</v>
@@ -8811,10 +8811,10 @@
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L25" s="8" t="s">
         <v>61</v>
@@ -8848,13 +8848,13 @@
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
@@ -8885,10 +8885,10 @@
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K27" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="L27" s="8" t="s">
         <v>61</v>
@@ -8922,10 +8922,10 @@
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K28" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="L28" s="8" t="s">
         <v>61</v>
@@ -8959,10 +8959,10 @@
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K29" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L29" s="8" t="s">
         <v>61</v>
@@ -8996,10 +8996,10 @@
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K30" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L30" s="8" t="s">
         <v>33</v>
@@ -9033,10 +9033,10 @@
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K31" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L31" s="8" t="s">
         <v>61</v>
@@ -9070,10 +9070,10 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K32" s="8" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="L32" s="8" t="s">
         <v>61</v>
@@ -9107,10 +9107,10 @@
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
       <c r="J33" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K33" s="8" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L33" s="8" t="s">
         <v>61</v>
@@ -9144,10 +9144,10 @@
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K34" s="8" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L34" s="8" t="s">
         <v>149</v>
@@ -9181,10 +9181,10 @@
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K35" s="8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L35" s="8" t="s">
         <v>61</v>
@@ -9218,10 +9218,10 @@
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K36" s="8" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L36" s="8" t="s">
         <v>61</v>
@@ -9255,10 +9255,10 @@
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K37" s="8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="L37" s="8" t="s">
         <v>61</v>
@@ -9292,7 +9292,7 @@
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K38" s="8" t="s">
         <v>85</v>
@@ -9329,7 +9329,7 @@
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K39" s="8" t="s">
         <v>86</v>
@@ -9366,7 +9366,7 @@
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K40" s="8" t="s">
         <v>87</v>
@@ -9403,7 +9403,7 @@
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>88</v>
@@ -9440,7 +9440,7 @@
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K42" s="8" t="s">
         <v>89</v>
@@ -9477,7 +9477,7 @@
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
       <c r="J43" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K43" s="8" t="s">
         <v>90</v>
@@ -9514,7 +9514,7 @@
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K44" s="8" t="s">
         <v>91</v>
@@ -9551,7 +9551,7 @@
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
       <c r="J45" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K45" s="8" t="s">
         <v>92</v>
@@ -9588,7 +9588,7 @@
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K46" s="8" t="s">
         <v>101</v>
@@ -9630,17 +9630,17 @@
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
       <c r="O47" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="P47" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="Q47" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="R47" s="10"/>
       <c r="S47" s="14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="T47" s="5"/>
       <c r="U47" s="5"/>
@@ -9669,17 +9669,17 @@
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
       <c r="O48" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q48" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="R48" s="10"/>
       <c r="S48" s="14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="T48" s="5"/>
       <c r="U48" s="5"/>
@@ -9708,17 +9708,17 @@
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
       <c r="O49" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="R49" s="10"/>
       <c r="S49" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="T49" s="5"/>
       <c r="U49" s="5"/>
@@ -9752,7 +9752,7 @@
       <c r="R50" s="10"/>
       <c r="S50" s="10"/>
       <c r="T50" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U50" s="8" t="s">
         <v>40</v>
@@ -9789,7 +9789,7 @@
       <c r="R51" s="10"/>
       <c r="S51" s="10"/>
       <c r="T51" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U51" s="8" t="s">
         <v>41</v>
@@ -9826,7 +9826,7 @@
       <c r="R52" s="10"/>
       <c r="S52" s="10"/>
       <c r="T52" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U52" s="8" t="s">
         <v>42</v>
@@ -9863,7 +9863,7 @@
       <c r="R53" s="10"/>
       <c r="S53" s="10"/>
       <c r="T53" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U53" s="8" t="s">
         <v>43</v>
@@ -9900,7 +9900,7 @@
       <c r="R54" s="10"/>
       <c r="S54" s="10"/>
       <c r="T54" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U54" s="8" t="s">
         <v>44</v>
@@ -9937,7 +9937,7 @@
       <c r="R55" s="10"/>
       <c r="S55" s="10"/>
       <c r="T55" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U55" s="8" t="s">
         <v>45</v>
@@ -9974,7 +9974,7 @@
       <c r="R56" s="10"/>
       <c r="S56" s="10"/>
       <c r="T56" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U56" s="8" t="s">
         <v>46</v>
@@ -10011,7 +10011,7 @@
       <c r="R57" s="10"/>
       <c r="S57" s="10"/>
       <c r="T57" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U57" s="8" t="s">
         <v>47</v>
@@ -10048,7 +10048,7 @@
       <c r="R58" s="10"/>
       <c r="S58" s="10"/>
       <c r="T58" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U58" s="8" t="s">
         <v>48</v>
@@ -10085,7 +10085,7 @@
       <c r="R59" s="10"/>
       <c r="S59" s="10"/>
       <c r="T59" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U59" s="8" t="s">
         <v>49</v>
@@ -10122,7 +10122,7 @@
       <c r="R60" s="10"/>
       <c r="S60" s="10"/>
       <c r="T60" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U60" s="5" t="s">
         <v>50</v>
@@ -10161,7 +10161,7 @@
       <c r="R61" s="10"/>
       <c r="S61" s="10"/>
       <c r="T61" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U61" s="8" t="s">
         <v>51</v>
@@ -10198,7 +10198,7 @@
       <c r="R62" s="10"/>
       <c r="S62" s="10"/>
       <c r="T62" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U62" s="8" t="s">
         <v>52</v>
@@ -10235,7 +10235,7 @@
       <c r="R63" s="10"/>
       <c r="S63" s="10"/>
       <c r="T63" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="U63" s="5" t="s">
         <v>53</v>
@@ -10306,47 +10306,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="35" t="s">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="34" t="s">
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
-      <c r="O1" s="37" t="s">
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="34" t="s">
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="42"/>
+      <c r="T1" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="U1" s="34"/>
-      <c r="V1" s="34"/>
-      <c r="W1" s="34"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="36" t="s">
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="Z1" s="36"/>
-      <c r="AA1" s="36"/>
-      <c r="AB1" s="36"/>
-      <c r="AC1" s="36"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
     </row>
     <row r="2" spans="1:29" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
@@ -10463,10 +10463,10 @@
       <c r="W3" s="5"/>
       <c r="X3" s="5"/>
       <c r="Y3" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="Z3" s="10" t="s">
         <v>221</v>
-      </c>
-      <c r="Z3" s="10" t="s">
-        <v>222</v>
       </c>
       <c r="AA3" s="10" t="s">
         <v>29</v>
@@ -10483,19 +10483,19 @@
         <v>117</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>251</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>252</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>251</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>252</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>29</v>
@@ -10505,20 +10505,20 @@
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P4" s="3" t="s">
         <v>37</v>
@@ -10529,7 +10529,7 @@
       <c r="R4" s="10"/>
       <c r="S4" s="10"/>
       <c r="T4" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="U4" s="5" t="s">
         <v>37</v>
@@ -10540,10 +10540,10 @@
       <c r="W4" s="5"/>
       <c r="X4" s="5"/>
       <c r="Y4" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Z4" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AA4" s="10" t="s">
         <v>29</v>
@@ -10558,19 +10558,19 @@
         <v>117</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>103</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>103</v>
@@ -10580,20 +10580,20 @@
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="L5" s="5" t="s">
         <v>61</v>
       </c>
       <c r="M5" s="5"/>
       <c r="N5" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P5" s="3" t="s">
         <v>13</v>
@@ -10604,7 +10604,7 @@
       <c r="R5" s="13"/>
       <c r="S5" s="10"/>
       <c r="T5" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="U5" s="5" t="s">
         <v>13</v>
@@ -10617,10 +10617,10 @@
       </c>
       <c r="X5" s="5"/>
       <c r="Y5" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Z5" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AA5" s="10" t="s">
         <v>31</v>
@@ -10635,19 +10635,19 @@
         <v>117</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>29</v>
@@ -10655,23 +10655,23 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L6" s="11" t="s">
         <v>29</v>
       </c>
       <c r="M6" s="11"/>
       <c r="N6" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="O6" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="O6" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="P6" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>39</v>
@@ -10679,10 +10679,10 @@
       <c r="R6" s="10"/>
       <c r="S6" s="10"/>
       <c r="T6" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="U6" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="V6" s="5" t="s">
         <v>39</v>
@@ -10691,13 +10691,13 @@
         <v>57</v>
       </c>
       <c r="X6" s="29" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Y6" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Z6" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AA6" s="10" t="s">
         <v>31</v>
@@ -10733,10 +10733,10 @@
       <c r="W7" s="5"/>
       <c r="X7" s="29"/>
       <c r="Y7" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Z7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AA7" s="32" t="s">
         <v>61</v>
@@ -10745,7 +10745,7 @@
         <v>12</v>
       </c>
       <c r="AC7" s="33" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
@@ -10774,7 +10774,7 @@
       <c r="W8" s="5"/>
       <c r="X8" s="5"/>
       <c r="Y8" s="10" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Z8" s="10" t="s">
         <v>28</v>
@@ -10792,19 +10792,19 @@
         <v>117</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D9" s="30" t="s">
         <v>29</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G9" s="31" t="s">
         <v>29</v>
@@ -10837,22 +10837,22 @@
         <v>117</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D10" s="30" t="s">
+        <v>249</v>
+      </c>
+      <c r="E10" s="31" t="s">
         <v>250</v>
       </c>
-      <c r="E10" s="31" t="s">
-        <v>251</v>
-      </c>
       <c r="F10" s="31" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
@@ -10883,19 +10883,19 @@
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
       <c r="E11" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>29</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
@@ -10960,10 +10960,10 @@
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K13" s="8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L13" s="8" t="s">
         <v>29</v>
@@ -10997,10 +10997,10 @@
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K14" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L14" s="8" t="s">
         <v>61</v>
@@ -11034,10 +11034,10 @@
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="L15" s="8" t="s">
         <v>61</v>
@@ -11071,10 +11071,10 @@
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K16" s="8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L16" s="8" t="s">
         <v>61</v>
@@ -11108,10 +11108,10 @@
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="L17" s="8" t="s">
         <v>103</v>
@@ -11145,10 +11145,10 @@
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="L18" s="8" t="s">
         <v>61</v>
@@ -11182,10 +11182,10 @@
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L19" s="8" t="s">
         <v>61</v>
@@ -11219,10 +11219,10 @@
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L20" s="8" t="s">
         <v>61</v>
@@ -11256,10 +11256,10 @@
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L21" s="8" t="s">
         <v>29</v>
@@ -11293,10 +11293,10 @@
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L22" s="8" t="s">
         <v>61</v>
@@ -11330,10 +11330,10 @@
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L23" s="8" t="s">
         <v>61</v>
@@ -11367,10 +11367,10 @@
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L24" s="8" t="s">
         <v>61</v>
@@ -11404,7 +11404,7 @@
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K25" s="8" t="s">
         <v>101</v>
@@ -11446,17 +11446,17 @@
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
       <c r="O26" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="R26" s="10"/>
       <c r="S26" s="14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="T26" s="5"/>
       <c r="U26" s="5"/>
@@ -11485,17 +11485,17 @@
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
       <c r="O27" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="R27" s="10"/>
       <c r="S27" s="14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="T27" s="5"/>
       <c r="U27" s="5"/>
@@ -11524,17 +11524,17 @@
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
       <c r="O28" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="R28" s="10"/>
       <c r="S28" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="T28" s="5"/>
       <c r="U28" s="5"/>
@@ -11568,7 +11568,7 @@
       <c r="R29" s="10"/>
       <c r="S29" s="10"/>
       <c r="T29" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="U29" s="8" t="s">
         <v>40</v>
@@ -11605,7 +11605,7 @@
       <c r="R30" s="10"/>
       <c r="S30" s="10"/>
       <c r="T30" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="U30" s="8" t="s">
         <v>41</v>
@@ -11642,7 +11642,7 @@
       <c r="R31" s="10"/>
       <c r="S31" s="10"/>
       <c r="T31" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="U31" s="8" t="s">
         <v>42</v>
@@ -11679,7 +11679,7 @@
       <c r="R32" s="10"/>
       <c r="S32" s="10"/>
       <c r="T32" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="U32" s="8" t="s">
         <v>43</v>
@@ -11716,7 +11716,7 @@
       <c r="R33" s="10"/>
       <c r="S33" s="10"/>
       <c r="T33" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="U33" s="8" t="s">
         <v>44</v>
@@ -11753,7 +11753,7 @@
       <c r="R34" s="10"/>
       <c r="S34" s="10"/>
       <c r="T34" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="U34" s="8" t="s">
         <v>45</v>
@@ -11790,7 +11790,7 @@
       <c r="R35" s="10"/>
       <c r="S35" s="10"/>
       <c r="T35" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="U35" s="8" t="s">
         <v>46</v>
@@ -11827,10 +11827,10 @@
       <c r="R36" s="10"/>
       <c r="S36" s="10"/>
       <c r="T36" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="U36" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="V36" s="8" t="s">
         <v>29</v>
@@ -11864,7 +11864,7 @@
       <c r="R37" s="10"/>
       <c r="S37" s="10"/>
       <c r="T37" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="U37" s="8" t="s">
         <v>47</v>
@@ -11901,7 +11901,7 @@
       <c r="R38" s="10"/>
       <c r="S38" s="10"/>
       <c r="T38" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="U38" s="8" t="s">
         <v>48</v>
@@ -11938,7 +11938,7 @@
       <c r="R39" s="10"/>
       <c r="S39" s="10"/>
       <c r="T39" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="U39" s="8" t="s">
         <v>49</v>
@@ -11975,7 +11975,7 @@
       <c r="R40" s="10"/>
       <c r="S40" s="10"/>
       <c r="T40" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="U40" s="5" t="s">
         <v>50</v>
@@ -12014,7 +12014,7 @@
       <c r="R41" s="10"/>
       <c r="S41" s="10"/>
       <c r="T41" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="U41" s="8" t="s">
         <v>51</v>
@@ -12051,7 +12051,7 @@
       <c r="R42" s="10"/>
       <c r="S42" s="10"/>
       <c r="T42" s="8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="U42" s="8" t="s">
         <v>52</v>
@@ -12088,7 +12088,7 @@
       <c r="R43" s="10"/>
       <c r="S43" s="10"/>
       <c r="T43" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="U43" s="5" t="s">
         <v>53</v>
@@ -12111,19 +12111,19 @@
         <v>117</v>
       </c>
       <c r="B44" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>255</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>256</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E44" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>29</v>
@@ -12133,20 +12133,20 @@
       </c>
       <c r="I44" s="3"/>
       <c r="J44" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L44" s="5" t="s">
         <v>29</v>
       </c>
       <c r="M44" s="5"/>
       <c r="N44" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O44" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>37</v>
@@ -12172,19 +12172,19 @@
         <v>117</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>104</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>104</v>
@@ -12194,20 +12194,20 @@
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="L45" s="5" t="s">
         <v>61</v>
       </c>
       <c r="M45" s="5"/>
       <c r="N45" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O45" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>13</v>
@@ -12233,22 +12233,22 @@
         <v>117</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D46" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F46" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>260</v>
-      </c>
       <c r="G46" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
@@ -12279,19 +12279,19 @@
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
       <c r="E47" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>29</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
@@ -12325,10 +12325,10 @@
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
       <c r="J48" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L48" s="8" t="s">
         <v>29</v>
@@ -12362,10 +12362,10 @@
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L49" s="8" t="s">
         <v>61</v>
@@ -12399,10 +12399,10 @@
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="L50" s="8" t="s">
         <v>61</v>
@@ -12436,10 +12436,10 @@
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L51" s="8" t="s">
         <v>61</v>
@@ -12473,10 +12473,10 @@
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K52" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L52" s="8" t="s">
         <v>104</v>
@@ -12510,10 +12510,10 @@
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K53" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L53" s="8" t="s">
         <v>61</v>
@@ -12547,10 +12547,10 @@
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K54" s="8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="L54" s="8" t="s">
         <v>61</v>
@@ -12584,10 +12584,10 @@
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K55" s="8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L55" s="8" t="s">
         <v>61</v>
@@ -12621,7 +12621,7 @@
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K56" s="8" t="s">
         <v>101</v>
@@ -12663,17 +12663,17 @@
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
       <c r="O57" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P57" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q57" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="R57" s="10"/>
       <c r="S57" s="14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="T57" s="5"/>
       <c r="U57" s="5"/>
@@ -12702,17 +12702,17 @@
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
       <c r="O58" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P58" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q58" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="R58" s="10"/>
       <c r="S58" s="14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="T58" s="5"/>
       <c r="U58" s="5"/>
@@ -12741,17 +12741,17 @@
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
       <c r="O59" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P59" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Q59" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="R59" s="10"/>
       <c r="S59" s="10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="T59" s="5"/>
       <c r="U59" s="5"/>
@@ -12801,26 +12801,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="35" t="s">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="34" t="s">
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="34"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
@@ -12871,19 +12871,19 @@
         <v>117</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>29</v>
@@ -12893,10 +12893,10 @@
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>282</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>283</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>29</v>
@@ -12917,19 +12917,19 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -12937,7 +12937,7 @@
         <v>117</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>11</v>
@@ -12946,7 +12946,7 @@
         <v>102</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>11</v>
@@ -12957,7 +12957,7 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>8</v>
@@ -12966,10 +12966,10 @@
         <v>29</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -12977,19 +12977,19 @@
         <v>117</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>29</v>
@@ -12997,19 +12997,19 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L6" s="5" t="s">
         <v>29</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -13017,36 +13017,36 @@
         <v>117</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>146</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N7" s="5"/>
     </row>
@@ -13055,36 +13055,36 @@
         <v>117</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>146</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N8" s="5"/>
     </row>
@@ -13093,36 +13093,36 @@
         <v>117</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>146</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="N9" s="5"/>
     </row>
@@ -13137,19 +13137,19 @@
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -13163,19 +13163,19 @@
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L11" s="5" t="s">
         <v>29</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -13189,19 +13189,19 @@
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N12" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -13215,19 +13215,19 @@
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -13241,19 +13241,19 @@
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
       <c r="J14" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -13267,7 +13267,7 @@
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
       <c r="J15" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K15" s="5" t="s">
         <v>28</v>
@@ -13276,7 +13276,7 @@
         <v>29</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N15" s="5"/>
     </row>
@@ -13285,19 +13285,19 @@
         <v>117</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>104</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>104</v>
@@ -13315,19 +13315,19 @@
         <v>117</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>104</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>104</v>
@@ -13346,19 +13346,19 @@
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>29</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
@@ -13371,19 +13371,19 @@
         <v>117</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>29</v>
@@ -13403,19 +13403,19 @@
         <v>117</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>29</v>
@@ -13435,22 +13435,22 @@
         <v>117</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>12</v>
@@ -13467,19 +13467,19 @@
         <v>117</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>148</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>148</v>
@@ -13499,22 +13499,22 @@
         <v>117</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>12</v>
@@ -13532,19 +13532,19 @@
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>29</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
